--- a/src/test/resources/com.exceldata/pwo2.1.xlsx
+++ b/src/test/resources/com.exceldata/pwo2.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15015" windowHeight="2805" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15120" windowHeight="6075" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
   <si>
     <t>EquipOrInstName</t>
   </si>
@@ -211,73 +211,70 @@
     <t>Breakdown</t>
   </si>
   <si>
-    <t>Sterile Room</t>
-  </si>
-  <si>
-    <t>Sterile Room-A</t>
-  </si>
-  <si>
-    <t>Equipment Check</t>
-  </si>
-  <si>
-    <t>Preventive Check</t>
-  </si>
-  <si>
-    <t>Microbiology Lab</t>
-  </si>
-  <si>
-    <t>Micro Analysis Lab</t>
-  </si>
-  <si>
-    <t>Quality Control Block</t>
-  </si>
-  <si>
-    <t>QC Block A</t>
-  </si>
-  <si>
-    <t>Temperature Fault</t>
-  </si>
-  <si>
-    <t>Temp Sensor Issue</t>
-  </si>
-  <si>
     <t>Paracetamol-500</t>
   </si>
   <si>
-    <t>Finished Product</t>
-  </si>
-  <si>
-    <t>FP-001</t>
-  </si>
-  <si>
-    <t>FP-500</t>
-  </si>
-  <si>
-    <t>R101</t>
-  </si>
-  <si>
-    <t>R101A</t>
-  </si>
-  <si>
     <t>Hyderabad</t>
   </si>
   <si>
     <t>Secunderabad</t>
   </si>
   <si>
-    <t>AC/D-101</t>
-  </si>
-  <si>
-    <t>AC/D-202</t>
-  </si>
-  <si>
-    <t>Autoclave</t>
-  </si>
-  <si>
-    <t>Autoclave-S</t>
-  </si>
-  <si>
-    <t>Manfacturer</t>
+    <t>Autoclave-A</t>
+  </si>
+  <si>
+    <t>Autoclave-C</t>
+  </si>
+  <si>
+    <t>Sterile Room-C</t>
+  </si>
+  <si>
+    <t>Equipment Check-C</t>
+  </si>
+  <si>
+    <t>Preventive Check-C</t>
+  </si>
+  <si>
+    <t>Microbiology Lab-C</t>
+  </si>
+  <si>
+    <t>Micro Analysis Lab-C</t>
+  </si>
+  <si>
+    <t>Quality Control Block-C</t>
+  </si>
+  <si>
+    <t>QC Block -C</t>
+  </si>
+  <si>
+    <t>Temperature Fault-C</t>
+  </si>
+  <si>
+    <t>Temp Sensor Issue-C</t>
+  </si>
+  <si>
+    <t>Finished Product-C</t>
+  </si>
+  <si>
+    <t>FP-00C</t>
+  </si>
+  <si>
+    <t>FP-50C</t>
+  </si>
+  <si>
+    <t>R10C</t>
+  </si>
+  <si>
+    <t>R101C</t>
+  </si>
+  <si>
+    <t>CC/D-101</t>
+  </si>
+  <si>
+    <t>CC/D-202</t>
+  </si>
+  <si>
+    <t>manufacturer</t>
   </si>
 </sst>
 </file>
@@ -783,73 +780,73 @@
     </row>
     <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>54</v>
